--- a/artfynd/A 18485-2026 artfynd.xlsx
+++ b/artfynd/A 18485-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3611,6 +3611,1253 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133931693</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>504533</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6703097</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133932744</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>504300</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6703045</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133930954</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>504505</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6703248</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133933035</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>504379</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6703300</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133931334</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>504548</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6703219</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133931392</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>504562</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6703215</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Födosöksspår gran</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133932856</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>504330</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6703215</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133932219</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>504291</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6703114</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spår av olika ålder på samma torrfura</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133931772</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>504470</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6703132</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133931051</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>504484</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6703232</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133932413</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>504246</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6703074</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18485-2026 artfynd.xlsx
+++ b/artfynd/A 18485-2026 artfynd.xlsx
@@ -3616,7 +3616,7 @@
         <v>133931693</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>133932744</v>
       </c>
       <c r="B29" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>133930954</v>
       </c>
       <c r="B30" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>133933035</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>133931334</v>
       </c>
       <c r="B32" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>133931392</v>
       </c>
       <c r="B33" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>133932856</v>
       </c>
       <c r="B34" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>133932219</v>
       </c>
       <c r="B35" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>133931772</v>
       </c>
       <c r="B36" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4636,10 +4636,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133931051</v>
+        <v>133932413</v>
       </c>
       <c r="B37" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504484</v>
+        <v>504246</v>
       </c>
       <c r="R37" t="n">
-        <v>6703232</v>
+        <v>6703074</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4748,10 +4748,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133932413</v>
+        <v>133931051</v>
       </c>
       <c r="B38" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4788,10 +4788,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504246</v>
+        <v>504484</v>
       </c>
       <c r="R38" t="n">
-        <v>6703074</v>
+        <v>6703232</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 18485-2026 artfynd.xlsx
+++ b/artfynd/A 18485-2026 artfynd.xlsx
@@ -3613,10 +3613,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133931693</v>
+        <v>133932744</v>
       </c>
       <c r="B28" t="n">
-        <v>57965</v>
+        <v>57962</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3624,16 +3624,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3644,7 +3644,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504533</v>
+        <v>504300</v>
       </c>
       <c r="R28" t="n">
-        <v>6703097</v>
+        <v>6703045</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3725,10 +3725,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133932744</v>
+        <v>133931693</v>
       </c>
       <c r="B29" t="n">
-        <v>57962</v>
+        <v>57965</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3736,16 +3736,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3756,7 +3756,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504300</v>
+        <v>504533</v>
       </c>
       <c r="R29" t="n">
-        <v>6703045</v>
+        <v>6703097</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 18485-2026 artfynd.xlsx
+++ b/artfynd/A 18485-2026 artfynd.xlsx
@@ -3613,10 +3613,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133932744</v>
+        <v>133931693</v>
       </c>
       <c r="B28" t="n">
-        <v>57962</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3624,16 +3624,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3644,7 +3644,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504300</v>
+        <v>504533</v>
       </c>
       <c r="R28" t="n">
-        <v>6703045</v>
+        <v>6703097</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3725,10 +3725,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133931693</v>
+        <v>133932744</v>
       </c>
       <c r="B29" t="n">
-        <v>57965</v>
+        <v>57972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3736,16 +3736,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3756,7 +3756,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504533</v>
+        <v>504300</v>
       </c>
       <c r="R29" t="n">
-        <v>6703097</v>
+        <v>6703045</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3840,7 +3840,7 @@
         <v>133930954</v>
       </c>
       <c r="B30" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>133933035</v>
       </c>
       <c r="B31" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>133931334</v>
       </c>
       <c r="B32" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>133931392</v>
       </c>
       <c r="B33" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>133932856</v>
       </c>
       <c r="B34" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>133932219</v>
       </c>
       <c r="B35" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>133931772</v>
       </c>
       <c r="B36" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>133932413</v>
       </c>
       <c r="B37" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>133931051</v>
       </c>
       <c r="B38" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 18485-2026 artfynd.xlsx
+++ b/artfynd/A 18485-2026 artfynd.xlsx
@@ -3840,7 +3840,7 @@
         <v>133930954</v>
       </c>
       <c r="B30" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133932856</v>
+        <v>133932219</v>
       </c>
       <c r="B34" t="n">
         <v>57972</v>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504330</v>
+        <v>504291</v>
       </c>
       <c r="R34" t="n">
-        <v>6703215</v>
+        <v>6703114</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4370,7 +4370,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Spår av olika ålder på samma torrfura</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4397,7 +4402,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133932219</v>
+        <v>133932856</v>
       </c>
       <c r="B35" t="n">
         <v>57972</v>
@@ -4437,10 +4442,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504291</v>
+        <v>504330</v>
       </c>
       <c r="R35" t="n">
-        <v>6703114</v>
+        <v>6703215</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4472,7 +4477,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4482,12 +4487,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spår av olika ålder på samma torrfura</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 18485-2026 artfynd.xlsx
+++ b/artfynd/A 18485-2026 artfynd.xlsx
@@ -4285,7 +4285,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133932219</v>
+        <v>133932856</v>
       </c>
       <c r="B34" t="n">
         <v>57972</v>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504291</v>
+        <v>504330</v>
       </c>
       <c r="R34" t="n">
-        <v>6703114</v>
+        <v>6703215</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4370,12 +4370,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Spår av olika ålder på samma torrfura</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4402,7 +4397,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133932856</v>
+        <v>133932219</v>
       </c>
       <c r="B35" t="n">
         <v>57972</v>
@@ -4442,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504330</v>
+        <v>504291</v>
       </c>
       <c r="R35" t="n">
-        <v>6703215</v>
+        <v>6703114</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4477,7 +4472,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4487,7 +4482,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spår av olika ålder på samma torrfura</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 18485-2026 artfynd.xlsx
+++ b/artfynd/A 18485-2026 artfynd.xlsx
@@ -4285,7 +4285,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133932219</v>
+        <v>133932856</v>
       </c>
       <c r="B34" t="n">
         <v>57972</v>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504291</v>
+        <v>504330</v>
       </c>
       <c r="R34" t="n">
-        <v>6703114</v>
+        <v>6703215</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4370,12 +4370,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Spår av olika ålder på samma torrfura</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4402,7 +4397,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133932856</v>
+        <v>133932219</v>
       </c>
       <c r="B35" t="n">
         <v>57972</v>
@@ -4442,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504330</v>
+        <v>504291</v>
       </c>
       <c r="R35" t="n">
-        <v>6703215</v>
+        <v>6703114</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4477,7 +4472,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4487,7 +4482,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spår av olika ålder på samma torrfura</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4636,7 +4636,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133932413</v>
+        <v>133931051</v>
       </c>
       <c r="B37" t="n">
         <v>57972</v>
@@ -4667,7 +4667,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504246</v>
+        <v>504484</v>
       </c>
       <c r="R37" t="n">
-        <v>6703074</v>
+        <v>6703232</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4748,7 +4748,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133931051</v>
+        <v>133932413</v>
       </c>
       <c r="B38" t="n">
         <v>57972</v>
@@ -4779,7 +4779,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4788,10 +4788,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504484</v>
+        <v>504246</v>
       </c>
       <c r="R38" t="n">
-        <v>6703232</v>
+        <v>6703074</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 18485-2026 artfynd.xlsx
+++ b/artfynd/A 18485-2026 artfynd.xlsx
@@ -3613,10 +3613,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133931693</v>
+        <v>133932744</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3624,16 +3624,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3644,7 +3644,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504533</v>
+        <v>504300</v>
       </c>
       <c r="R28" t="n">
-        <v>6703097</v>
+        <v>6703045</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3725,10 +3725,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133932744</v>
+        <v>133931693</v>
       </c>
       <c r="B29" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3736,16 +3736,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3756,7 +3756,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504300</v>
+        <v>504533</v>
       </c>
       <c r="R29" t="n">
-        <v>6703045</v>
+        <v>6703097</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3840,7 +3840,7 @@
         <v>133930954</v>
       </c>
       <c r="B30" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133931051</v>
+        <v>133932413</v>
       </c>
       <c r="B37" t="n">
         <v>57972</v>
@@ -4667,7 +4667,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504484</v>
+        <v>504246</v>
       </c>
       <c r="R37" t="n">
-        <v>6703232</v>
+        <v>6703074</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4748,7 +4748,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133932413</v>
+        <v>133931051</v>
       </c>
       <c r="B38" t="n">
         <v>57972</v>
@@ -4779,7 +4779,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4788,10 +4788,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504246</v>
+        <v>504484</v>
       </c>
       <c r="R38" t="n">
-        <v>6703074</v>
+        <v>6703232</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 18485-2026 artfynd.xlsx
+++ b/artfynd/A 18485-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103803356</v>
+        <v>104139070</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504348.5251868414</v>
+        <v>504362</v>
       </c>
       <c r="R2" t="n">
-        <v>6703265.395628016</v>
+        <v>6703267</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103803158</v>
+        <v>104139734</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504398.7295074461</v>
+        <v>504456</v>
       </c>
       <c r="R3" t="n">
-        <v>6703416.864083141</v>
+        <v>6703102</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,22 +839,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103803429</v>
+        <v>104139186</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +882,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504328.3489011432</v>
+        <v>504346</v>
       </c>
       <c r="R4" t="n">
-        <v>6703200.269087286</v>
+        <v>6703244</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,22 +937,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +969,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103803279</v>
+        <v>103803094</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504372.1884717544</v>
+        <v>504465</v>
       </c>
       <c r="R5" t="n">
-        <v>6703305.865914399</v>
+        <v>6703569</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1038,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103803149</v>
+        <v>103803133</v>
       </c>
       <c r="B6" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504395.7524467445</v>
+        <v>504416</v>
       </c>
       <c r="R6" t="n">
-        <v>6703427.710297708</v>
+        <v>6703476</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1136,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,37 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103803510</v>
+        <v>103803213</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504284.4618406583</v>
+        <v>504375</v>
       </c>
       <c r="R7" t="n">
-        <v>6703132.64729911</v>
+        <v>6703342</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,19 +1234,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,37 +1263,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103803674</v>
+        <v>103803279</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1299,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504284.0232459211</v>
+        <v>504373</v>
       </c>
       <c r="R8" t="n">
-        <v>6703085.791209972</v>
+        <v>6703305</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,19 +1332,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,15 +1361,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103803213</v>
+        <v>104140091</v>
       </c>
       <c r="B9" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504374.6137720204</v>
+        <v>504557</v>
       </c>
       <c r="R9" t="n">
-        <v>6703342.85789533</v>
+        <v>6703227</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1537,22 +1427,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,37 +1459,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103803094</v>
+        <v>103803158</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504464.7357636802</v>
+        <v>504399</v>
       </c>
       <c r="R10" t="n">
-        <v>6703568.839535299</v>
+        <v>6703417</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,19 +1528,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,16 +1560,11 @@
         <v>103803181</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1733,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504386.9044175568</v>
+        <v>504387</v>
       </c>
       <c r="R11" t="n">
-        <v>6703391.697735887</v>
+        <v>6703392</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1766,19 +1626,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,37 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103803133</v>
+        <v>103803356</v>
       </c>
       <c r="B12" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1846,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504415.9478982502</v>
+        <v>504349</v>
       </c>
       <c r="R12" t="n">
-        <v>6703475.079201849</v>
+        <v>6703265</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,19 +1724,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,19 +1753,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104139523</v>
+        <v>103803429</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1959,10 +1789,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504303.3272138548</v>
+        <v>504329</v>
       </c>
       <c r="R13" t="n">
-        <v>6703054.741121347</v>
+        <v>6703200</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1989,22 +1819,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,19 +1851,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104139247</v>
+        <v>103803510</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2072,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504312.0195173448</v>
+        <v>504284</v>
       </c>
       <c r="R14" t="n">
-        <v>6703222.93692892</v>
+        <v>6703133</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2102,22 +1917,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,37 +1949,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104139462</v>
+        <v>103803674</v>
       </c>
       <c r="B15" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2185,10 +1985,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504283.5082180313</v>
+        <v>504284</v>
       </c>
       <c r="R15" t="n">
-        <v>6703103.546466931</v>
+        <v>6703086</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,22 +2015,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,37 +2047,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104139412</v>
+        <v>104139130</v>
       </c>
       <c r="B16" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504307.6326956908</v>
+        <v>504353</v>
       </c>
       <c r="R16" t="n">
-        <v>6703173.118055381</v>
+        <v>6703235</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2331,19 +2116,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,19 +2145,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104139898</v>
+        <v>104139247</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2411,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504480.0859985555</v>
+        <v>504313</v>
       </c>
       <c r="R17" t="n">
-        <v>6703139.295783376</v>
+        <v>6703223</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2444,19 +2214,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,37 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104139734</v>
+        <v>104139481</v>
       </c>
       <c r="B18" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2524,10 +2279,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504456.4191854413</v>
+        <v>504277</v>
       </c>
       <c r="R18" t="n">
-        <v>6703101.782238721</v>
+        <v>6703080</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2557,19 +2312,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2596,19 +2341,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104140132</v>
+        <v>104139523</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2637,10 +2377,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504557.0630556563</v>
+        <v>504303</v>
       </c>
       <c r="R19" t="n">
-        <v>6703210.906941455</v>
+        <v>6703055</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2670,19 +2410,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2709,37 +2439,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104139437</v>
+        <v>104139594</v>
       </c>
       <c r="B20" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2750,10 +2475,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504297.3016901242</v>
+        <v>504317</v>
       </c>
       <c r="R20" t="n">
-        <v>6703136.608216673</v>
+        <v>6703076</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2783,19 +2508,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,37 +2537,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104139186</v>
+        <v>104139680</v>
       </c>
       <c r="B21" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2863,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504346.0806264261</v>
+        <v>504461</v>
       </c>
       <c r="R21" t="n">
-        <v>6703244.185231344</v>
+        <v>6703107</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2896,19 +2606,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,19 +2635,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104139594</v>
+        <v>104139898</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2976,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>504317.1348022604</v>
+        <v>504480</v>
       </c>
       <c r="R22" t="n">
-        <v>6703075.966121422</v>
+        <v>6703139</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3009,19 +2704,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,37 +2733,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104140091</v>
+        <v>104140132</v>
       </c>
       <c r="B23" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3089,10 +2769,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504557.0425751412</v>
+        <v>504558</v>
       </c>
       <c r="R23" t="n">
-        <v>6703227.182572661</v>
+        <v>6703211</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3122,19 +2802,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,19 +2831,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104139130</v>
+        <v>133930954</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3195,20 +2860,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gagnef, Dlr</t>
+          <t>Ershols klack, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504352.0193577271</v>
+        <v>504505</v>
       </c>
       <c r="R24" t="n">
-        <v>6703235.314784291</v>
+        <v>6703248</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3232,22 +2896,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,27 +2926,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104139481</v>
+        <v>103803149</v>
       </c>
       <c r="B25" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,21 +2949,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3315,10 +2974,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>504277.1144426445</v>
+        <v>504395</v>
       </c>
       <c r="R25" t="n">
-        <v>6703079.371182244</v>
+        <v>6703428</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3345,22 +3004,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3387,15 +3036,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104139070</v>
+        <v>104139412</v>
       </c>
       <c r="B26" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,21 +3047,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3428,10 +3072,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504362.8500661577</v>
+        <v>504308</v>
       </c>
       <c r="R26" t="n">
-        <v>6703266.399248146</v>
+        <v>6703173</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3461,19 +3105,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,15 +3134,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104139680</v>
+        <v>104139437</v>
       </c>
       <c r="B27" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3516,21 +3145,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3541,10 +3170,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504460.3653082292</v>
+        <v>504297</v>
       </c>
       <c r="R27" t="n">
-        <v>6703106.719269337</v>
+        <v>6703137</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3574,19 +3203,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3613,10 +3232,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133932744</v>
+        <v>104139462</v>
       </c>
       <c r="B28" t="n">
-        <v>57972</v>
+        <v>75428</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3624,42 +3243,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ershols klack, Dlr</t>
+          <t>Gagnef, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504300</v>
+        <v>504284</v>
       </c>
       <c r="R28" t="n">
-        <v>6703045</v>
+        <v>6703104</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3683,22 +3298,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2022-10-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3713,39 +3318,39 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133931693</v>
+        <v>133931051</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3765,10 +3370,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504533</v>
+        <v>504484</v>
       </c>
       <c r="R29" t="n">
-        <v>6703097</v>
+        <v>6703232</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3800,7 +3405,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3810,7 +3415,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3837,45 +3442,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133930954</v>
+        <v>133931471</v>
       </c>
       <c r="B30" t="n">
-        <v>79366</v>
+        <v>57972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ershols klack, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504505</v>
+        <v>504576</v>
       </c>
       <c r="R30" t="n">
-        <v>6703248</v>
+        <v>6703203</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3907,7 +3517,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3917,7 +3527,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3944,27 +3554,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133933035</v>
+        <v>133931590</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3975,7 +3585,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3984,10 +3594,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504379</v>
+        <v>504582</v>
       </c>
       <c r="R31" t="n">
-        <v>6703300</v>
+        <v>6703228</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4019,7 +3629,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4029,7 +3639,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4056,10 +3666,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133931334</v>
+        <v>133931864</v>
       </c>
       <c r="B32" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,27 +3677,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4096,10 +3706,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504548</v>
+        <v>504480</v>
       </c>
       <c r="R32" t="n">
-        <v>6703219</v>
+        <v>6703102</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4131,7 +3741,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4141,7 +3751,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4168,27 +3778,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133931392</v>
+        <v>133931986</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4199,7 +3809,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4208,10 +3818,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504562</v>
+        <v>504382</v>
       </c>
       <c r="R33" t="n">
-        <v>6703215</v>
+        <v>6703103</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4243,7 +3853,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4253,12 +3863,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Födosöksspår gran</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4285,14 +3890,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133932856</v>
+        <v>133932219</v>
       </c>
       <c r="B34" t="n">
         <v>57972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4325,10 +3930,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504330</v>
+        <v>504291</v>
       </c>
       <c r="R34" t="n">
-        <v>6703215</v>
+        <v>6703114</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4360,7 +3965,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4370,7 +3975,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Spår av olika ålder på samma torrfura</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4397,14 +4007,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133932219</v>
+        <v>133932413</v>
       </c>
       <c r="B35" t="n">
         <v>57972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4437,10 +4047,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504291</v>
+        <v>504246</v>
       </c>
       <c r="R35" t="n">
-        <v>6703114</v>
+        <v>6703074</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4472,7 +4082,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4482,12 +4092,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spår av olika ålder på samma torrfura</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4514,10 +4119,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133931772</v>
+        <v>133932744</v>
       </c>
       <c r="B36" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4525,37 +4130,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4564,10 +4159,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504470</v>
+        <v>504300</v>
       </c>
       <c r="R36" t="n">
-        <v>6703132</v>
+        <v>6703045</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4599,7 +4194,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4609,7 +4204,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4636,14 +4231,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133932413</v>
+        <v>133932856</v>
       </c>
       <c r="B37" t="n">
         <v>57972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4676,10 +4271,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504246</v>
+        <v>504330</v>
       </c>
       <c r="R37" t="n">
-        <v>6703074</v>
+        <v>6703215</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4711,7 +4306,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4721,7 +4316,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4748,10 +4343,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133931051</v>
+        <v>133931392</v>
       </c>
       <c r="B38" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4759,16 +4354,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4779,7 +4374,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4788,10 +4383,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504484</v>
+        <v>504562</v>
       </c>
       <c r="R38" t="n">
-        <v>6703232</v>
+        <v>6703215</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4823,7 +4418,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4833,7 +4428,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Födosöksspår gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4857,6 +4457,464 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133931693</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>504533</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6703097</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>133933035</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>504379</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6703300</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>133931334</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>504548</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6703219</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>133931772</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ershols klack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>504470</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6703132</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18485-2026 artfynd.xlsx
+++ b/artfynd/A 18485-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104139070</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104139734</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104139186</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103803094</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103803133</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103803213</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103803279</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104140091</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103803158</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103803181</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,6 +1805,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103803356</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103803429</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103803510</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103803674</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104139130</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2240,6 +2320,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104139247</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2338,6 +2423,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104139481</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104139523</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2534,6 +2629,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104139594</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,6 +2732,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104139680</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2730,6 +2835,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104139898</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2828,6 +2938,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104140132</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2935,6 +3050,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133930954</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3033,6 +3153,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103803149</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3131,6 +3256,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104139412</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3229,6 +3359,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104139437</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3327,6 +3462,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104139462</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3439,6 +3579,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133931051</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3551,6 +3696,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133931471</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3663,6 +3813,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133931590</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3775,6 +3930,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133931864</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3887,6 +4047,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133931986</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4004,6 +4169,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133932219</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4116,6 +4286,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133932413</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4228,6 +4403,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133932744</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4340,6 +4520,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133932856</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4457,6 +4642,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133931392</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4569,6 +4759,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133931693</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4681,6 +4876,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133933035</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4793,6 +4993,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133931334</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4915,8 +5120,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133931772</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>